--- a/research/brics_universities/output/BRICS_universities_china.xlsx
+++ b/research/brics_universities/output/BRICS_universities_china.xlsx
@@ -558,10 +558,10 @@
         <v>134</v>
       </c>
       <c r="G5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Fu Mengyin (付梦印)</t>
+          <t>Yang Yixin (杨益新)</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -7084,15 +7084,16 @@
       <c r="AD35" s="4" t="inlineStr"/>
       <c r="AE35" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>• Сайт njust.edu.cn закрыт антибот-защитой — страницы руководства и контактов не открылись
-• Руководство взято из китайской Википедии, не подтверждено на 2025–2026 — перепроверить
 • TW-1B (2015) в nanosats.eu приписан Шанхайскому центру микроспутников — не учтён
-• Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере</t>
+• Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере
+• ИСПРАВЛЕНО: ректор (校长) с сентября 2025 — Ян Исинь (杨益新), назначен МПИ КНР вместо Фу Мэнъиня; подтверждено новостями официального сайта zs.njust.edu.cn (31.08.2026, 10.09.2026). Партсекретарь Лу Гуйбинь (路贵斌) подтверждён там же (сент. 2026)
+• Перепроверка: Руководство исправлено и подтверждено на новостном сайте вуза (сент. 2026): президент Ян Исинь вместо Фу Мэнъиня; контакты международного отдела по-прежнему не открываются</t>
         </is>
       </c>
       <c r="AG35" s="4" t="inlineStr">
@@ -7106,7 +7107,10 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government
 • Https://en.wikipedia.org/wiki/Seven_Sons_of_National_Defence
 • Nanosats.eu export (local nanosats.csv)
-• Https://gjc.njust.edu.cn/</t>
+• Https://gjc.njust.edu.cn/
+• Https://zs.njust.edu.cn/3550/list.htm
+• Https://zs.njust.edu.cn/a9/a2/c3550a371106/page.htm
+• Https://www.edu.cn/ke_yan_yu_fa_zhan/gao_xiao_cheng_guo/gao_xiao_zi_xun/202509/t20250922_2691129.shtml</t>
         </is>
       </c>
       <c r="AH35" s="4" t="inlineStr">
@@ -14669,7 +14673,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Fu Mengyin (付梦印)</t>
+          <t>Yang Yixin (杨益新)</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -14726,15 +14730,16 @@
       <c r="AD35" s="4" t="inlineStr"/>
       <c r="AE35" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>• Сайт njust.edu.cn закрыт антибот-защитой — страницы руководства и контактов не открылись
-• Руководство взято из китайской Википедии, не подтверждено на 2025–2026 — перепроверить
 • TW-1B (2015) в nanosats.eu приписан Шанхайскому центру микроспутников — не учтён
-• Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере</t>
+• Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере
+• ИСПРАВЛЕНО: ректор (校长) с сентября 2025 — Ян Исинь (杨益新), назначен МПИ КНР вместо Фу Мэнъиня; подтверждено новостями официального сайта zs.njust.edu.cn (31.08.2026, 10.09.2026). Партсекретарь Лу Гуйбинь (路贵斌) подтверждён там же (сент. 2026)
+• Перепроверка: Руководство исправлено и подтверждено на новостном сайте вуза (сент. 2026): президент Ян Исинь вместо Фу Мэнъиня; контакты международного отдела по-прежнему не открываются</t>
         </is>
       </c>
       <c r="AG35" s="4" t="inlineStr">
@@ -14748,7 +14753,10 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government
 • Https://en.wikipedia.org/wiki/Seven_Sons_of_National_Defence
 • Nanosats.eu export (local nanosats.csv)
-• Https://gjc.njust.edu.cn/</t>
+• Https://gjc.njust.edu.cn/
+• Https://zs.njust.edu.cn/3550/list.htm
+• Https://zs.njust.edu.cn/a9/a2/c3550a371106/page.htm
+• Https://www.edu.cn/ke_yan_yu_fa_zhan/gao_xiao_cheng_guo/gao_xiao_zi_xun/202509/t20250922_2691129.shtml</t>
         </is>
       </c>
       <c r="AH35" s="4" t="inlineStr">
@@ -22924,7 +22932,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>130 Meilong Road, Shanghai 200237, China</t>
+          <t>130 Meilong Road, Shanghai 200237, China (上海市梅陇路130号, 邮编 200237)</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -22947,7 +22955,7 @@
       <c r="M85" s="4" t="inlineStr"/>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>+86-21-64252952 (Office of International Cooperation and Exchange)</t>
+          <t>+86-21-64252952 (Office of International Cooperation and Exchange, по сниппету); коммутатор/справочная +86-21-64253300</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -23004,14 +23012,16 @@
       </c>
       <c r="AE85" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF85" s="4" t="inlineStr">
         <is>
           <t>• Сайт Отдела международного сотрудничества (ice.ecust.edu.cn) доступен только из кампуса; e-mail iao@ecust.edu.cn и телефон взяты из поискового сниппета этой страницы, не проверены открытием — перепроверить
 • По тому же сниппету директором отдела указан Li Yongsheng (李永生, ysli@ecust.edu.cn, 021-64252435) — дата не известна, в addressee не внесено
-• По одному быстрому поиску («&lt;название&gt; 卫星 发射») собственных запущенных спутников не найдено (LIGHT-проверка)</t>
+• По одному быстрому поиску («&lt;название&gt; 卫星 发射») собственных запущенных спутников не найдено (LIGHT-проверка)
+• Ректор, адрес и номер справочной (64253300) подтверждены на официальном сайте www.ecust.edu.cn 04.10.2026; сайты cie./ice.ecust.edu.cn отдают HTTP 483 (только из кампуса) — e-mail отдела не перепроверен
+• Перепроверка: Ректор Сюань Фучжэнь, адрес и телефон справочной подтверждены на сайте 04.10.2026; e-mail международного отдела по-прежнему только из сниппета</t>
         </is>
       </c>
       <c r="AG85" s="4" t="inlineStr">
@@ -23607,7 +23617,8 @@
           <t>• Сайты njnu.edu.cn / nnu.edu.cn блокируют автоматический доступ (HTTP 412) — адрес, телефон и e-mail не верифицированы
 • Ректор Хуан Хэ (академик CAE) — с марта 2026; партсекретарь Шан Цинфэй — с января 2026 (по новостям ScienceNet со ссылкой на официальный сайт)
 • По данным поиска (не проверено): адрес 1 Wenyuan Road, Qixia District, Nanjing 210023; кабинет начальника отдела междунар. сотрудничества +86-25-83598530
-• Спутников не найдено (один быстрый поиск)</t>
+• Спутников не найдено (один быстрый поиск)
+• Перепроверка: Все домены njnu.edu.cn (www, en, gjc) по-прежнему отдают анти-бот-защиту HTTP 412 (04.10.2026); обход не выполнялся, данные не изменены</t>
         </is>
       </c>
       <c r="AG89" s="4" t="inlineStr">
@@ -24300,7 +24311,11 @@
           <t>https://www.cdut.edu.cn</t>
         </is>
       </c>
-      <c r="P94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr">
+        <is>
+          <t>Xu Qiang (许强)</t>
+        </is>
+      </c>
       <c r="Q94" s="4" t="inlineStr">
         <is>
           <t>President (校长)</t>
@@ -24346,7 +24361,9 @@
           <t>• Сайт cdut.edu.cn блокирует автоматический доступ (HTTP 412) — контакты и ректор не верифицированы
 • Партсекретарь Шэнь Хоумин назначен 08.05.2026 (новость ScienceNet со ссылкой на вуз). Ректор по данным поиска — Сюй Цян (许强, с окт. 2023), на официальной странице не проверено
 • Космическое направление: планетология (сведения из одного поиска); собственных спутников не найдено
-• В рейтингах QS 2027 и THE 2027 не представлен</t>
+• В рейтингах QS 2027 и THE 2027 не представлен
+• Повторная проверка 04.10.2026: все поддомены cdut.edu.cn (www, news, gjc, /en) отдают HTTP 412 (антибот) или недоступны. Ректор Сюй Цян (许强) внесён по сайту провинциального комитета Цзюсань (93sc.gov.cn) о назначении в окт. 2023; на 2025–2026 официально не подтверждён
+• Перепроверка: Сайт вуза по-прежнему блокирует доступ (412); ректор Сюй Цян внесён по сообщению 93sc.gov.cn (2023), контакты не найдены — уровень low сохранён</t>
         </is>
       </c>
       <c r="AG94" s="4" t="inlineStr">
@@ -24356,7 +24373,8 @@
 • Https://m.163.com/dy/article/KVMPBEEK05218435.html
 • Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
 • Https://www.shanghairanking.cn/rankings/bcur/2026
-• Https://www.ecfr.gov/current/title-15/part-744/appendix-Supplement%20No.%204%20to%20Part%20744</t>
+• Https://www.ecfr.gov/current/title-15/part-744/appendix-Supplement%20No.%204%20to%20Part%20744
+• Https://www.93sc.gov.cn/view/40661.html</t>
         </is>
       </c>
       <c r="AH94" s="4" t="inlineStr">
@@ -25712,14 +25730,15 @@
       <c r="AD103" s="4" t="inlineStr"/>
       <c r="AE103" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF103" s="4" t="inlineStr">
         <is>
-          <t>• Сайт Отдела международного сотрудничества (foreign.ujs.edu.cn) закрыт для внешнего доступа (только WebVPN); e-mail/телефон отдела и имя директора не получены
-• Английская страница Contact Us содержит только адрес
-• По одному быстрому поиску («&lt;название&gt; 卫星 发射») собственных запущенных спутников не найдено (LIGHT-проверка)</t>
+          <t>• Сайт Отдела международного сотрудничества (foreign.ujs.edu.cn) и сайты iucae./admission.ujs.edu.cn закрыты для внешнего доступа (483/503); e-mail/телефон отдела и имя директора не получены
+• Английская страница Contact Us и главная страница ujs.edu.cn содержат только адрес (301 Xuefu Road, Zhenjiang 212013) — публичного e-mail нет; канал связи нужно искать вручную
+• По одному быстрому поиску («&lt;название&gt; 卫星 发射») собственных запущенных спутников не найдено (LIGHT-проверка)
+• Перепроверка: Президент Цзоу Сяобо и адрес подтверждены на ujs.edu.cn 04.10.2026 (новости сент. 2026); e-mail и телефон по-прежнему не найдены</t>
         </is>
       </c>
       <c r="AG103" s="4" t="inlineStr">
@@ -25945,11 +25964,30 @@
           <t>No. 30 Puzhu South Road, Jiangbei New Area, Nanjing, Jiangsu 211816, P.R. China</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr"/>
-      <c r="K105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>president@njtech.edu.cn</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Jiang Juncheng
+President
+Ящик «校长信箱» (обращения к президенту университета)
+Обращение: Dear President Jiang,</t>
+        </is>
+      </c>
       <c r="L105" s="4" t="inlineStr"/>
-      <c r="M105" s="4" t="inlineStr"/>
-      <c r="N105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>president@njtech.edu.cn</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>+86 25 5813 9023</t>
+        </is>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>https://www.njtech.edu.cn (EN: http://en.njtech.edu.cn)</t>
@@ -25993,23 +26031,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD105" s="4" t="inlineStr"/>
+      <c r="AD105" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE105" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF105" s="4" t="inlineStr">
         <is>
-          <t>• Сайт международного отдела (ico.njtech.edu.cn) доступен только из кампусной сети, англ. сайт отвечает ошибкой 483 — e-mail международного отдела и телефон не получены
+          <t>• Сайт международного отдела (ico.njtech.edu.cn) и телефонный справочник (hqc.njtech.edu.cn) доступны только из кампусной сети (ошибка 483) — отдельный e-mail международного отдела не получен; использован ящик президента со страницы «校长信箱»
+• Учёное звание президента (Prof.) на странице руководства не указано — по общедоступным данным он профессор
 • Собственных спутников не найдено (одна быстрая проверка по запросу «&lt;название&gt; 卫星 发射»)
-• В QS2027 не входит</t>
+• В QS2027 не входит
+• Перепроверка: Президент Цзян Цзюньчэн и партсекретарь подтверждены на njtech.edu.cn 04.10.2026; добавлены e-mail president@njtech.edu.cn и тел. 025-58139023 со страницы «校长信箱»</t>
         </is>
       </c>
       <c r="AG105" s="4" t="inlineStr">
         <is>
           <t>• Https://www.njtech.edu.cn/
 • Https://www.njtech.edu.cn/xxgk/xrld.htm
+• Https://www.njtech.edu.cn/xzxx.htm
 • Local the.html (THE WUR 2027 data)</t>
         </is>
       </c>
@@ -27176,7 +27221,11 @@
           <t>https://www.yzu.edu.cn</t>
         </is>
       </c>
-      <c r="P113" s="4" t="inlineStr"/>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>Liu Qiaoquan (刘巧泉)</t>
+        </is>
+      </c>
       <c r="Q113" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -27218,17 +27267,20 @@
       </c>
       <c r="AF113" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт и все поддомены защищены антибот-системой (JS-челлендж, HTTP 412) — контакты, руководство и международный отдел не проверены
-• По Википедии (не официальный источник, актуальность не подтверждена): ректор Яо Цзяньлинь (姚建林), партсекретарь Лю Цяоцюань (刘巧泉) — перед рассылкой проверить
-• Космическая проверка ограничена базой nanosats.eu и официальными страницами: квота веб-поиска сессии исчерпана (200/200); спутников вуза не найдено
-• Не входит в QS2027; в Entity List США не найден</t>
+          <t>• Официальный сайт и поддомены (www., english.) по-прежнему закрыты антибот-системой (HTTP 412) или недоступны — контакты и международный отдел не проверены
+• ИСПРАВЛЕНО: данные Википедии устарели. По Синьхуа (Цзянсу, 20.12.2024) ректор — Лю Цяоцюань (刘巧泉, ранее проректор), партсекретарь — Дин Цзяньнин (丁建宁, ранее ректор). Изменения после 12.2024 не проверены на официальном сайте
+• Адрес — по уставу вуза, цитируемому в Википедии; не подтверждён на официальном сайте
+• Космическая проверка ограничена базой nanosats.eu; спутников вуза не найдено
+• Не входит в QS2027; в Entity List США не найден
+• Перепроверка: Сайт по-прежнему закрыт антиботом; руководство исправлено по Синьхуа (12.2024): ректор Лю Цяоцюань, партсекретарь Дин Цзяньнин; контактов нет</t>
         </is>
       </c>
       <c r="AG113" s="4" t="inlineStr">
         <is>
           <t>• Https://www.yzu.edu.cn/ (blocked: anti-bot JS / HTTP 412)
+• Http://js.news.cn/20241220/d609d3a96a014948a8ccc33cd6e20877/c.html
+• Https://www.acabridge.cn/zxhz/202412/t20241223_2647664.shtml
 • Https://zh.wikipedia.org/wiki/扬州大学
-• Https://m.163.com/dy/article_cambrian/KVN9UVMJ0536JW7T.html
 • Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking
 • Https://www.shanghairanking.cn/rankings/bcur/2026
 • Https://www.ecfr.gov/current/title-15/part-744/appendix-Supplement%20No.%204%20to%20Part%20744</t>
@@ -27239,7 +27291,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AI113" s="4" t="inlineStr"/>
+      <c r="AI113" s="4" t="inlineStr">
+        <is>
+          <t>Ding Jianning (丁建宁)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -30641,7 +30697,8 @@
         <is>
           <t>• Официальный сайт www.bistu.edu.cn недоступен (DNS/503 через curl и WebFetch) — контакты не проверены
 • Руководство — по китайской Википедии (назначения август 2023), перепроверить на 2026 год
-• Проверка спутников: поиск в вебе не выполнен (общая квота WebSearch исчерпана); по базе nanosats.eu совпадений нет — satellites_launched=0 не подтверждено полноценно</t>
+• Проверка спутников: поиск в вебе не выполнен (общая квота WebSearch исчерпана); по базе nanosats.eu совпадений нет — satellites_launched=0 не подтверждено полноценно
+• Перепроверка: Сайт bistu.edu.cn (включая en.) недоступен через прокси (curl — нет соединения, WebFetch 503) 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG136" s="4" t="inlineStr">
@@ -30912,7 +30969,8 @@
           <t>• Все сайты cjlu.edu.cn (включая ino.cjlu.edu.cn) блокируют доступ (HTTP 412) — контакты не проверены
 • По поисковому индексу официального сайта: ящик международного отдела intoff@cjlu.edu.cn, тел. 0571-86836028, адрес 258 Xueyuan Street, Qiantang District, Hangzhou 310018 — НЕ проверено открытием страницы, сверить перед рассылкой
 • Руководство подтверждено по СМИ 2024–2025 гг. (Сюй Цзянжун — секретарь парткома с 09.2024; Дай Даосинь — проректор, руководящий администрацией с 08.2025); данных за 2026 г. нет
-• Быстрая проверка не выявила спутников вуза</t>
+• Быстрая проверка не выявила спутников вуза
+• Перепроверка: 04.10.2026: cjlu.edu.cn и ino.cjlu.edu.cn по-прежнему отвечают HTTP 412 (антибот) — данные не изменены</t>
         </is>
       </c>
       <c r="AG138" s="4" t="inlineStr">
@@ -30984,14 +31042,18 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>8 Daxue Road, Yichang, Hubei 443002, China</t>
+          <t>Office of International Cooperation and Exchange, Room J1504, China Three Gorges University, 8 Daxue Road, Yichang, Hubei 443002, China</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
       <c r="L139" s="4" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>+86 717 639 2033; +86 717 639 2097 (International Office)</t>
+        </is>
+      </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
           <t>https://www.ctgu.edu.cn</t>
@@ -31034,20 +31096,23 @@
       <c r="AD139" s="4" t="inlineStr"/>
       <c r="AE139" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF139" s="4" t="inlineStr">
         <is>
-          <t>• На главной странице сайта Отдела международного сотрудничества (dir.ctgu.edu.cn) e-mail, телефон и имя директора не опубликованы
+          <t>• Ректор Хуан Янь и секретарь парткома Ван Цзяньпин подтверждены на странице «Действующее руководство» официального сайта
+• Отдел международного сотрудничества: директор Шангуань Янь (上官燕), каб. J1504, тел. 0717-6392033 / 6392097 (официальные страницы dir.ctgu.edu.cn); e-mail на сайте не опубликован — нужен иной канал
 • Космическая проверка не выполнена: исчерпан лимит веб-поиска сессии; в выгрузке nanosats.eu вуз не найден
-• В QS2027 и THE2027 не найден</t>
+• В QS2027 и THE2027 не найден
+• Перепроверка: 04.10.2026: руководство подтверждено на сайте; добавлены директор международного отдела, его телефоны и кабинет; e-mail по-прежнему не опубликован</t>
         </is>
       </c>
       <c r="AG139" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ctgu.edu.cn/xxgk2/xrld.htm
-• Http://dir.ctgu.edu.cn/
+• Https://dir.ctgu.edu.cn/gywm/jgsz.htm
+• Https://dir.ctgu.edu.cn/gywm/lxwm.htm
 • Https://www.shanghairanking.cn/rankings/bcur/2026</t>
         </is>
       </c>
@@ -32949,7 +33014,8 @@
           <t>• Сайт hubu.edu.cn недоступен (503/обрыв соединения через прокси, в т.ч. через WebFetch) — контакты и руководство не проверены по официальным страницам
 • По «Википедии» (ред. 08.09.2026): должность ректора вакантна; секретарь парткома Лю Цзяньпин (刘建平) указан до сентября 2026 г., преемник не назван — требует проверки
 • Космическая проверка не проведена (исчерпана квота поиска); данных о спутниках нет
-• В QS2027 и найденном списке THE2027 не обнаружен</t>
+• В QS2027 и найденном списке THE2027 не обнаружен
+• Перепроверка: Сайт hubu.edu.cn и англ. поддомены по-прежнему недоступны (04.10.2026, 503/сброс соединения); данные не изменены</t>
         </is>
       </c>
       <c r="AG152" s="4" t="inlineStr">
@@ -33047,7 +33113,8 @@
         <is>
           <t>• Официальный сайт www.hbut.edu.cn и поддомены недоступны из среды исследования (DNS/прокси отклоняют соединение) — контакты, руководство и адрес не проверены; требуется ручная проверка
 • Лимит веб-поиска исчерпан — спутниковая проверка выполнена только по nanosats.eu (упоминаний нет)
-• В рейтингах QS2027 (топ-500) и THE не найден; в US Entity List не найден</t>
+• В рейтингах QS2027 (топ-500) и THE не найден; в US Entity List не найден
+• Перепроверка: Сайт hbut.edu.cn и англ. поддомены по-прежнему недоступны (04.10.2026, 502/DNS); данные не изменены</t>
         </is>
       </c>
       <c r="AG153" s="4" t="inlineStr">
@@ -34012,7 +34079,7 @@
       <c r="M160" s="4" t="inlineStr"/>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>+86-871-65916977 (President's Office)</t>
+          <t>+86-871-65916977 (President's Office); +86-871-65915366 / 65915166 (Office of International Cooperation and Exchange, 对外合作交流处)</t>
         </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
@@ -34057,15 +34124,16 @@
       <c r="AD160" s="4" t="inlineStr"/>
       <c r="AE160" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF160" s="4" t="inlineStr">
         <is>
-          <t>• Сайт международного отдела (global.kust.edu.cn / global.kmust.edu.cn) блокирует внешний доступ (HTTP 403); e-mail и имя директора не получены
+          <t>• Сайт международного отдела (global.kust.edu.cn) блокирует внешний доступ (HTTP 403); e-mail и имя директора не получены. Международные связи курирует проректор Цзян Ехуа (蒋业华), помощник ректора Цао Чжэн (曹峥)
 • Активно работает с Южной и Юго-Восточной Азией (центр исследований АСЕАН)
 • По одному быстрому поиску («&lt;название&gt; 卫星 发射») собственных запущенных спутников не найдено (LIGHT-проверка)
-• В QS2027 и THE2027 не найден</t>
+• В QS2027 и THE2027 не найден
+• Перепроверка: Ректор Ян Бинь, партсекретарь Тан Цзяхуа, адрес и телефоны (вкл. международный отдел) подтверждены на kust.edu.cn 04.10.2026; e-mail не найден (global.kust.edu.cn — 403)</t>
         </is>
       </c>
       <c r="AG160" s="4" t="inlineStr">
@@ -34073,7 +34141,8 @@
           <t>• Https://www.kust.edu.cn/xxgk/dzld.htm
 • Https://www.kust.edu.cn/xxgk/jgsz1/lxdh.htm
 • Https://global.kust.edu.cn/ (403 blocked)
-• Https://www.shanghairanking.cn/rankings/bcur/2026</t>
+• Https://www.shanghairanking.cn/rankings/bcur/2026
+• Https://www.kust.edu.cn/xxgk/jgsz1/lxdh.htm</t>
         </is>
       </c>
       <c r="AH160" s="4" t="inlineStr">
@@ -34083,7 +34152,7 @@
       </c>
       <c r="AI160" s="4" t="inlineStr">
         <is>
-          <t>Tang Jiahua (唐家华)</t>
+          <t>Tang Jiahua (唐家华), Party Secretary</t>
         </is>
       </c>
     </row>
@@ -34133,13 +34202,28 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Dalian, Liaoning, China (Huanghe Road and Xishan Lake campuses)</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr"/>
-      <c r="K161" s="4" t="inlineStr"/>
+          <t>Liaoning Normal University, No. 850 Huanghe Road, Shahekou District, Dalian, Liaoning 116029, China (辽宁省大连市沙河口区黄河路850号)</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>dzoffice@lnnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Luo Wenbo
+President
+President's mailbox (校长邮箱)
+Обращение: Dear President Luo,</t>
+        </is>
+      </c>
       <c r="L161" s="4" t="inlineStr"/>
-      <c r="M161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>dzoffice@lnnu.edu.cn</t>
+        </is>
+      </c>
       <c r="N161" s="4" t="inlineStr"/>
       <c r="O161" s="4" t="inlineStr">
         <is>
@@ -34180,22 +34264,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD161" s="4" t="inlineStr"/>
+      <c r="AD161" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE161" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF161" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт www.lnnu.edu.cn недоступен (HTTP 503 / таймаут через curl и WebFetch) — контакты, адрес и руководство не проверены по официальным источникам
-• Руководство указано только по китайской Википедии (без даты) — обязательно перепроверить перед рассылкой
-• Проверка спутников: поиск в вебе не выполнен (общая квота WebSearch исчерпана); по базе nanosats.eu совпадений нет — satellites_launched=0 не подтверждено полноценно</t>
+          <t>• Ректор (校长) Ло Вэньбо и партсекретарь Лю Хун подтверждены на официальной странице «党政领导» (страница с новостями от 09.2026)
+• Dzoffice@lnnu.edu.cn — официальный «校长邮箱» (ящик ректора) из подвала сайта; адрес — из подвала официального сайта
+• Телефон и e-mail отдела международного сотрудничества (国际合作与交流处) не извлечены; есть Колледж международного образования gjy.lnnu.edu.cn (почта cie925@163.com — сторонний домен, не использована)
+• Проверка спутников: по базе nanosats.eu совпадений нет; веб-поиск не выполнялся — satellites_launched=0 не подтверждено полноценно
+• Перепроверка: Сайт стал доступен: руководство, адрес и ящик ректора подтверждены на официальном сайте 04.10.2026</t>
         </is>
       </c>
       <c r="AG161" s="4" t="inlineStr">
         <is>
-          <t>• Https://zh.wikipedia.org/wiki/辽宁师范大学
+          <t>• Https://www.lnnu.edu.cn/xxgk/dzld.htm
+• Https://www2023.lnnu.edu.cn/bgdh/dqxzjg.htm
+• Https://gjy.lnnu.edu.cn/
 • Https://www.nanosats.eu/database
 • Https://www.shanghairanking.cn/rankings/bcur/2026
 • Https://www.ecfr.gov/current/title-15/part-744/appendix-Supplement%20No.%204%20to%20Part%20744</t>
@@ -35136,7 +35228,8 @@
         <is>
           <t>• Официальный сайт www.nwnu.edu.cn блокирует автоматический доступ (HTTP 412, антибот-защита), поддомены недоступны через прокси — контакты, руководство и адрес не проверены; требуется ручная проверка в браузере
 • Лимит веб-поиска исчерпан — спутниковая проверка выполнена только по nanosats.eu (упоминаний нет)
-• В рейтингах QS2027 (топ-500) и THE не найден; в US Entity List не найден</t>
+• В рейтингах QS2027 (топ-500) и THE не найден; в US Entity List не найден
+• Перепроверка: 04.10.2026: сайт и поддомены nwnu.edu.cn по-прежнему закрыты антибот-защитой (HTTP 412) или недоступны; данные не изменены</t>
         </is>
       </c>
       <c r="AG168" s="4" t="inlineStr">
@@ -35560,7 +35653,8 @@
           <t>• Официальный сайт недоступен (403 для прямых запросов, 503 через fetch) — руководство, e-mail и международный отдел не проверены
 • Википедия указывает ректора Чжан Кая (张凯) без даты — актуальность не подтверждена, в поле не внесено
 • Космическая проверка ограничена базой nanosats.eu и официальными страницами: квота веб-поиска сессии исчерпана (200/200); спутников вуза не найдено
-• Не входит в QS2027 и THE2027; в Entity List США не найден</t>
+• Не входит в QS2027 и THE2027; в Entity List США не найден
+• Перепроверка: Сайт qut.edu.cn недоступен (403 для http, 503 через WebFetch, english. — нет соединения) 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG171" s="4" t="inlineStr">
@@ -35996,7 +36090,7 @@
       </c>
       <c r="AD174" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="AE174" s="4" t="inlineStr">
@@ -37014,7 +37108,8 @@
           <t>• Все сайты *.sylu.edu.cn недоступны из нашей сети (таймаут/503) — адрес, телефоны и e-mail не верифицированы, поля оставлены пустыми
 • По данным поиска (не проверено на официальной странице): отдел междунар. сотрудничества — тел. +86-24-24686047, адрес Nanping Zhonglu 6, Hunnan, Shenyang 110159; Институт междунар. образования gjjyxy@sylu.edu.cn (+86-24-24681016 — набор из русскоязычных стран)
 • Собственных спутников не найдено (в вузе хранится резервный экземпляр «Дунфанхун-1», но это не разработка вуза)
-• Вуз оборонного профиля (бывший Шэньянский промышленный институт), в QS/THE не ранжирован; руководство подтверждено новостью Минобразования провинции Ляонин от 01.05.2026</t>
+• Вуз оборонного профиля (бывший Шэньянский промышленный институт), в QS/THE не ранжирован; руководство подтверждено новостью Минобразования провинции Ляонин от 01.05.2026
+• Перепроверка: 04.10.2026: *.sylu.edu.cn недоступны (502/DNS), сайт Департамента образования провинции Ляонин тоже — данные не изменены</t>
         </is>
       </c>
       <c r="AG181" s="4" t="inlineStr">
@@ -38267,8 +38362,16 @@
           <t>https://www.wit.edu.cn</t>
         </is>
       </c>
-      <c r="P190" s="4" t="inlineStr"/>
-      <c r="Q190" s="4" t="inlineStr"/>
+      <c r="P190" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Zhang Yanduo (张彦铎)</t>
+        </is>
+      </c>
+      <c r="Q190" s="4" t="inlineStr">
+        <is>
+          <t>President (校长); Deputy Party Secretary</t>
+        </is>
+      </c>
       <c r="R190" s="4" t="inlineStr"/>
       <c r="S190" s="4" t="inlineStr"/>
       <c r="T190" s="4" t="inlineStr">
@@ -38301,15 +38404,18 @@
       </c>
       <c r="AF190" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт wit.edu.cn и все поддомены недоступны (503 / сброс соединения) — руководство и контакты проверить не удалось
-• По Википедии ректор — Zhang Yanduo (张彦铎), но данные 2025–2026 гг. не подтверждены, поэтому поле head_name пустое
+          <t>• Официальный сайт wit.edu.cn и все поддомены недоступны (503 / сброс соединения, повторно 04.10.2026) — контакты (e-mail, телефон, международный отдел) проверить не удалось
+• Ректор Zhang Yanduo (张彦铎) назначен 24.03.2025 решением парткома провинции Хубэй (акаде­мические СМИ 2025 г. со ссылкой на WIT; официальная новость news.wit.edu.cn видна только в поисковой выдаче)
 • Адрес взят из Википедии (кампус Учан) — уточнить индекс
-• Собственных спутников не найдено (одна быстрая проверка по запросу «&lt;название&gt; 卫星 发射»)</t>
+• Собственных спутников не найдено (одна быстрая проверка по запросу «&lt;название&gt; 卫星 发射»)
+• Перепроверка: Ректор Чжан Яньдо (назначен 24.03.2025) подтверждён публикациями 2025 г. со ссылкой на WIT; сайт wit.edu.cn по-прежнему недоступен (503) — контакты не проверены</t>
         </is>
       </c>
       <c r="AG190" s="4" t="inlineStr">
         <is>
-          <t>Https://zh.wikipedia.org/wiki/武汉工程大学 (official site wit.edu.cn unreachable)</t>
+          <t>• Https://zh.wikipedia.org/wiki/武汉工程大学 (official site wit.edu.cn unreachable)
+• Https://www.acabridge.cn/zxhz/202503/t20250325_2660464.shtml
+• Https://m.thepaper.cn/newsDetail_forward_30492832</t>
         </is>
       </c>
       <c r="AH190" s="4" t="inlineStr">
